--- a/data/2023_HRSWURN_Tables.xlsx
+++ b/data/2023_HRSWURN_Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARSMNSPP4DFG174\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reyno061\Documents\GitHub\Git_demo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57E4D5B-FAEA-4C0F-9AEA-2ABB4A1B0A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85589D05-56B0-4396-916F-006E7A3B1F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="838" firstSheet="15" activeTab="26" xr2:uid="{BC65913E-1809-4B59-BE8F-B0869AF7DC59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="838" firstSheet="15" activeTab="16" xr2:uid="{BC65913E-1809-4B59-BE8F-B0869AF7DC59}"/>
   </bookViews>
   <sheets>
     <sheet name="Entry List" sheetId="1" r:id="rId1"/>
@@ -4950,7 +4950,7 @@
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5839,6 +5839,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5872,14 +5875,18 @@
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="126">
@@ -14240,14 +14247,14 @@
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="339" t="s">
+      <c r="B3" s="340" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="339"/>
-      <c r="D3" s="339" t="s">
+      <c r="C3" s="340"/>
+      <c r="D3" s="340" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="339"/>
+      <c r="E3" s="340"/>
       <c r="F3" s="31" t="s">
         <v>71</v>
       </c>
@@ -14265,14 +14272,14 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="2"/>
-      <c r="B4" s="339" t="s">
+      <c r="B4" s="340" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="339"/>
-      <c r="D4" s="339" t="s">
+      <c r="C4" s="340"/>
+      <c r="D4" s="340" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="339"/>
+      <c r="E4" s="340"/>
       <c r="F4" s="31" t="s">
         <v>77</v>
       </c>
@@ -14321,961 +14328,961 @@
     </row>
     <row r="6" spans="1:11" ht="15.75" thickTop="1">
       <c r="A6" s="3" t="s">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="B6" s="35">
-        <v>53.327749999999988</v>
+        <v>83.748083333333327</v>
       </c>
       <c r="C6" s="6">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D6" s="35">
-        <v>59.002716353076856</v>
+        <v>59.226638883714223</v>
       </c>
       <c r="E6" s="6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F6" s="35">
-        <v>30.938296296296294</v>
+        <v>28.56474444444445</v>
       </c>
       <c r="G6" s="35">
-        <v>103.58700606060606</v>
+        <v>75.897532121212123</v>
       </c>
       <c r="H6" s="35">
-        <v>14.960898755279603</v>
+        <v>13.732791252065244</v>
       </c>
       <c r="I6" s="35">
-        <v>2.416666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="3" t="s">
-        <v>10</v>
+        <v>198</v>
       </c>
       <c r="B7" s="35">
-        <v>57.294250000000005</v>
+        <v>80.846249999999998</v>
       </c>
       <c r="C7" s="6">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D7" s="35">
-        <v>58.796364843546087</v>
+        <v>59.158417528300511</v>
       </c>
       <c r="E7" s="6">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F7" s="35">
-        <v>30.724922222222226</v>
+        <v>28.204299999999996</v>
       </c>
       <c r="G7" s="35">
-        <v>101.27801474747476</v>
+        <v>78.135725252525248</v>
       </c>
       <c r="H7" s="35">
-        <v>15.333620398589836</v>
+        <v>13.742071189925115</v>
       </c>
       <c r="I7" s="35">
-        <v>2.6666666666666665</v>
+        <v>0.5</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="3" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="B8" s="35">
-        <v>77.313999999999993</v>
+        <v>80.302166666666665</v>
       </c>
       <c r="C8" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D8" s="35">
-        <v>60.359755350245706</v>
+        <v>59.835166783820078</v>
       </c>
       <c r="E8" s="6">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F8" s="35">
-        <v>29.557744444444445</v>
+        <v>26.90684814814815</v>
       </c>
       <c r="G8" s="35">
-        <v>82.314778383838387</v>
+        <v>73.999904646464657</v>
       </c>
       <c r="H8" s="35">
-        <v>13.935174297862989</v>
+        <v>14.570805800221935</v>
       </c>
       <c r="I8" s="35">
-        <v>0.91666666666666674</v>
+        <v>0.75</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="3" t="s">
-        <v>12</v>
+        <v>299</v>
       </c>
       <c r="B9" s="35">
-        <v>66.725499999999997</v>
+        <v>77.73</v>
       </c>
       <c r="C9" s="6">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D9" s="35">
-        <v>60.705903136759709</v>
+        <v>59.906319719428815</v>
       </c>
       <c r="E9" s="6">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F9" s="35">
-        <v>27.318003703703702</v>
+        <v>27.89363333333333</v>
       </c>
       <c r="G9" s="35">
-        <v>70.954667878787888</v>
+        <v>70.693373737373733</v>
       </c>
       <c r="H9" s="35">
-        <v>15.359741396318265</v>
+        <v>14.160135152983383</v>
       </c>
       <c r="I9" s="35">
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="3" t="s">
-        <v>13</v>
+        <v>297</v>
       </c>
       <c r="B10" s="35">
-        <v>68.316749999999999</v>
+        <v>77.376249999999985</v>
       </c>
       <c r="C10" s="6">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D10" s="35">
-        <v>59.839723124104147</v>
+        <v>59.336275056492923</v>
       </c>
       <c r="E10" s="6">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F10" s="35">
-        <v>29.888262962962958</v>
+        <v>28.862666666666669</v>
       </c>
       <c r="G10" s="35">
-        <v>79.32630040404041</v>
+        <v>68.463613333333328</v>
       </c>
       <c r="H10" s="35">
-        <v>15.019490611552243</v>
+        <v>13.743616389190937</v>
       </c>
       <c r="I10" s="35">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="3" t="s">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="B11" s="35">
-        <v>71.912083333333328</v>
+        <v>77.313999999999993</v>
       </c>
       <c r="C11" s="6">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D11" s="35">
-        <v>60.526440056034239</v>
+        <v>60.359755350245706</v>
       </c>
       <c r="E11" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F11" s="35">
-        <v>28.625966666666663</v>
+        <v>29.557744444444445</v>
       </c>
       <c r="G11" s="35">
-        <v>76.069046262626259</v>
+        <v>82.314778383838387</v>
       </c>
       <c r="H11" s="35">
-        <v>15.136460421924697</v>
+        <v>13.935174297862989</v>
       </c>
       <c r="I11" s="35">
-        <v>0.41666666666666663</v>
+        <v>0.91666666666666674</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="3" t="s">
-        <v>392</v>
+        <v>296</v>
       </c>
       <c r="B12" s="35">
-        <v>74.044666666666657</v>
+        <v>76.911916666666656</v>
       </c>
       <c r="C12" s="6">
+        <v>7</v>
+      </c>
+      <c r="D12" s="35">
+        <v>60.308581724776019</v>
+      </c>
+      <c r="E12" s="6">
         <v>13</v>
       </c>
-      <c r="D12" s="35">
-        <v>59.822542970804172</v>
-      </c>
-      <c r="E12" s="6">
-        <v>24</v>
-      </c>
       <c r="F12" s="35">
-        <v>35.249481481481489</v>
+        <v>27.946374074074072</v>
       </c>
       <c r="G12" s="35">
-        <v>72.35039979797979</v>
+        <v>74.851016565656579</v>
       </c>
       <c r="H12" s="35">
-        <v>14.418577748598979</v>
+        <v>14.079840797841342</v>
       </c>
       <c r="I12" s="35">
-        <v>0.5</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="3" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B13" s="35">
-        <v>68.705250000000007</v>
+        <v>76.731083333333331</v>
       </c>
       <c r="C13" s="6">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D13" s="35">
-        <v>61.060730239977097</v>
+        <v>60.204103486756672</v>
       </c>
       <c r="E13" s="6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F13" s="35">
-        <v>29.230225925925922</v>
+        <v>27.597225925925922</v>
       </c>
       <c r="G13" s="35">
-        <v>73.291786666666667</v>
+        <v>72.766333535353539</v>
       </c>
       <c r="H13" s="35">
-        <v>15.977784230606188</v>
+        <v>14.145561872825617</v>
       </c>
       <c r="I13" s="35">
-        <v>0.41666666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="3" t="s">
-        <v>285</v>
+        <v>201</v>
       </c>
       <c r="B14" s="35">
-        <v>73.194083333333339</v>
+        <v>76.307916666666671</v>
       </c>
       <c r="C14" s="6">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D14" s="35">
-        <v>61.291336589342755</v>
+        <v>60.442985241537144</v>
       </c>
       <c r="E14" s="6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F14" s="35">
-        <v>29.543370370370369</v>
+        <v>27.230888888888888</v>
       </c>
       <c r="G14" s="35">
-        <v>75.297615959595959</v>
+        <v>71.52477616161616</v>
       </c>
       <c r="H14" s="35">
-        <v>14.183966627451802</v>
+        <v>14.518644353487161</v>
       </c>
       <c r="I14" s="35">
-        <v>0.33333333333333331</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="3" t="s">
-        <v>286</v>
+        <v>205</v>
       </c>
       <c r="B15" s="35">
-        <v>68.228999999999999</v>
+        <v>76.02558333333333</v>
       </c>
       <c r="C15" s="6">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D15" s="35">
-        <v>60.010467967815742</v>
+        <v>59.837394187749403</v>
       </c>
       <c r="E15" s="6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F15" s="35">
-        <v>30.554777777777772</v>
+        <v>30.962892592592596</v>
       </c>
       <c r="G15" s="35">
-        <v>62.940830303030296</v>
+        <v>76.963881616161615</v>
       </c>
       <c r="H15" s="35">
-        <v>14.178932504528932</v>
+        <v>14.793447756485783</v>
       </c>
       <c r="I15" s="35">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B16" s="35">
-        <v>73.601583333333338</v>
+        <v>75.098916666666668</v>
       </c>
       <c r="C16" s="6">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D16" s="35">
-        <v>60.954140662393655</v>
+        <v>61.872624431941468</v>
       </c>
       <c r="E16" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F16" s="35">
-        <v>29.87211111111111</v>
+        <v>29.685337037037034</v>
       </c>
       <c r="G16" s="35">
-        <v>75.401342828282822</v>
+        <v>81.377085656565654</v>
       </c>
       <c r="H16" s="35">
-        <v>14.828097256278506</v>
+        <v>14.555126617717677</v>
       </c>
       <c r="I16" s="35">
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="3" t="s">
-        <v>198</v>
+        <v>288</v>
       </c>
       <c r="B17" s="35">
-        <v>80.846249999999998</v>
+        <v>74.37191666666665</v>
       </c>
       <c r="C17" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D17" s="35">
-        <v>59.158417528300511</v>
+        <v>59.845963446585024</v>
       </c>
       <c r="E17" s="6">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F17" s="35">
-        <v>28.204299999999996</v>
+        <v>33.052185185185188</v>
       </c>
       <c r="G17" s="35">
-        <v>78.135725252525248</v>
+        <v>76.934839797979791</v>
       </c>
       <c r="H17" s="35">
-        <v>13.742071189925115</v>
+        <v>14.945050777805585</v>
       </c>
       <c r="I17" s="35">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="3" t="s">
-        <v>288</v>
+        <v>392</v>
       </c>
       <c r="B18" s="35">
-        <v>74.37191666666665</v>
+        <v>74.044666666666657</v>
       </c>
       <c r="C18" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" s="35">
-        <v>59.845963446585024</v>
+        <v>59.822542970804172</v>
       </c>
       <c r="E18" s="6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F18" s="35">
-        <v>33.052185185185188</v>
+        <v>35.249481481481489</v>
       </c>
       <c r="G18" s="35">
-        <v>76.934839797979791</v>
+        <v>72.35039979797979</v>
       </c>
       <c r="H18" s="35">
-        <v>14.945050777805585</v>
+        <v>14.418577748598979</v>
       </c>
       <c r="I18" s="35">
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B19" s="35">
-        <v>71.732333333333315</v>
-      </c>
-      <c r="C19" s="6">
-        <v>21</v>
-      </c>
-      <c r="D19" s="35">
-        <v>60.308675729478388</v>
-      </c>
-      <c r="E19" s="6">
-        <v>12</v>
-      </c>
-      <c r="F19" s="35">
-        <v>28.869518518518518</v>
-      </c>
-      <c r="G19" s="35">
-        <v>76.121485050505044</v>
-      </c>
-      <c r="H19" s="35">
-        <v>14.85193909807032</v>
-      </c>
-      <c r="I19" s="35">
-        <v>0.25</v>
+      <c r="A19" s="352" t="s">
+        <v>316</v>
+      </c>
+      <c r="B19" s="353">
+        <v>73.71008333333333</v>
+      </c>
+      <c r="C19" s="354">
+        <v>14</v>
+      </c>
+      <c r="D19" s="353">
+        <v>60.127627800663277</v>
+      </c>
+      <c r="E19" s="354">
+        <v>16</v>
+      </c>
+      <c r="F19" s="353">
+        <v>28.661070370370371</v>
+      </c>
+      <c r="G19" s="353">
+        <v>68.852888686868695</v>
+      </c>
+      <c r="H19" s="353">
+        <v>14.556307224927883</v>
+      </c>
+      <c r="I19" s="353">
+        <v>0.66666666666666663</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B20" s="35">
-        <v>69.735916666666654</v>
+        <v>73.601583333333338</v>
       </c>
       <c r="C20" s="6">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D20" s="35">
-        <v>62.572483664509093</v>
+        <v>60.954140662393655</v>
       </c>
       <c r="E20" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F20" s="35">
-        <v>28.776481481481483</v>
+        <v>29.87211111111111</v>
       </c>
       <c r="G20" s="35">
-        <v>79.034913131313132</v>
+        <v>75.401342828282822</v>
       </c>
       <c r="H20" s="35">
-        <v>14.551249978286643</v>
+        <v>14.828097256278506</v>
       </c>
       <c r="I20" s="35">
-        <v>0.25</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B21" s="35">
-        <v>75.098916666666668</v>
+        <v>73.194083333333339</v>
       </c>
       <c r="C21" s="6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D21" s="35">
-        <v>61.872624431941468</v>
+        <v>61.291336589342755</v>
       </c>
       <c r="E21" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21" s="35">
-        <v>29.685337037037034</v>
+        <v>29.543370370370369</v>
       </c>
       <c r="G21" s="35">
-        <v>81.377085656565654</v>
+        <v>75.297615959595959</v>
       </c>
       <c r="H21" s="35">
-        <v>14.555126617717677</v>
+        <v>14.183966627451802</v>
       </c>
       <c r="I21" s="35">
-        <v>0.25</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="3" t="s">
-        <v>119</v>
+        <v>294</v>
       </c>
       <c r="B22" s="35">
-        <v>80.302166666666665</v>
+        <v>72.705500000000001</v>
       </c>
       <c r="C22" s="6">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D22" s="35">
-        <v>59.835166783820078</v>
+        <v>59.259090407690564</v>
       </c>
       <c r="E22" s="6">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F22" s="35">
-        <v>26.90684814814815</v>
+        <v>28.271255555555555</v>
       </c>
       <c r="G22" s="35">
-        <v>73.999904646464657</v>
+        <v>75.477445858585853</v>
       </c>
       <c r="H22" s="35">
-        <v>14.570805800221935</v>
+        <v>14.37758632313551</v>
       </c>
       <c r="I22" s="35">
-        <v>0.75</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="3" t="s">
-        <v>200</v>
+        <v>298</v>
       </c>
       <c r="B23" s="35">
-        <v>83.748083333333327</v>
+        <v>72.547333333333327</v>
       </c>
       <c r="C23" s="6">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D23" s="35">
-        <v>59.226638883714223</v>
+        <v>59.839671819006689</v>
       </c>
       <c r="E23" s="6">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F23" s="35">
-        <v>28.56474444444445</v>
+        <v>29.086929629629633</v>
       </c>
       <c r="G23" s="35">
-        <v>75.897532121212123</v>
+        <v>65.699258383838384</v>
       </c>
       <c r="H23" s="35">
-        <v>13.732791252065244</v>
+        <v>14.004239416515457</v>
       </c>
       <c r="I23" s="35">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="3" t="s">
-        <v>201</v>
+        <v>117</v>
       </c>
       <c r="B24" s="35">
-        <v>76.307916666666671</v>
+        <v>71.912083333333328</v>
       </c>
       <c r="C24" s="6">
+        <v>19</v>
+      </c>
+      <c r="D24" s="35">
+        <v>60.526440056034239</v>
+      </c>
+      <c r="E24" s="6">
         <v>9</v>
       </c>
-      <c r="D24" s="35">
-        <v>60.442985241537144</v>
-      </c>
-      <c r="E24" s="6">
-        <v>10</v>
-      </c>
       <c r="F24" s="35">
-        <v>27.230888888888888</v>
+        <v>28.625966666666663</v>
       </c>
       <c r="G24" s="35">
-        <v>71.52477616161616</v>
+        <v>76.069046262626259</v>
       </c>
       <c r="H24" s="35">
-        <v>14.518644353487161</v>
+        <v>15.136460421924697</v>
       </c>
       <c r="I24" s="35">
-        <v>0.66666666666666663</v>
+        <v>0.41666666666666663</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B25" s="35">
-        <v>71.47508333333333</v>
+        <v>71.904250000000005</v>
       </c>
       <c r="C25" s="6">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D25" s="35">
-        <v>60.737063540315638</v>
+        <v>59.516027511885113</v>
       </c>
       <c r="E25" s="6">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="F25" s="35">
-        <v>26.698999999999998</v>
+        <v>28.920703703703705</v>
       </c>
       <c r="G25" s="35">
-        <v>68.266619595959597</v>
+        <v>76.237274141414147</v>
       </c>
       <c r="H25" s="35">
-        <v>14.293362329456256</v>
+        <v>13.902003516161558</v>
       </c>
       <c r="I25" s="35">
-        <v>0.41666666666666669</v>
+        <v>1</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B26" s="35">
-        <v>70.678166666666655</v>
+        <v>71.732333333333315</v>
       </c>
       <c r="C26" s="6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D26" s="35">
-        <v>61.554938036835843</v>
+        <v>60.308675729478388</v>
       </c>
       <c r="E26" s="6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F26" s="35">
-        <v>27.568885185185188</v>
+        <v>28.869518518518518</v>
       </c>
       <c r="G26" s="35">
-        <v>77.136589292929287</v>
+        <v>76.121485050505044</v>
       </c>
       <c r="H26" s="35">
-        <v>14.943490633322106</v>
+        <v>14.85193909807032</v>
       </c>
       <c r="I26" s="35">
-        <v>0.41666666666666663</v>
+        <v>0.25</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="3" t="s">
-        <v>205</v>
+        <v>292</v>
       </c>
       <c r="B27" s="35">
-        <v>76.02558333333333</v>
+        <v>71.47508333333333</v>
       </c>
       <c r="C27" s="6">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D27" s="35">
-        <v>59.837394187749403</v>
+        <v>60.737063540315638</v>
       </c>
       <c r="E27" s="6">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F27" s="35">
-        <v>30.962892592592596</v>
+        <v>26.698999999999998</v>
       </c>
       <c r="G27" s="35">
-        <v>76.963881616161615</v>
+        <v>68.266619595959597</v>
       </c>
       <c r="H27" s="35">
-        <v>14.793447756485783</v>
+        <v>14.293362329456256</v>
       </c>
       <c r="I27" s="35">
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="3" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="B28" s="35">
-        <v>70.221166666666647</v>
+        <v>70.678166666666655</v>
       </c>
       <c r="C28" s="6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D28" s="35">
-        <v>60.211715871321665</v>
+        <v>61.554938036835843</v>
       </c>
       <c r="E28" s="6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F28" s="35">
-        <v>24.013485185185186</v>
+        <v>27.568885185185188</v>
       </c>
       <c r="G28" s="35">
-        <v>70.05685656565656</v>
+        <v>77.136589292929287</v>
       </c>
       <c r="H28" s="35">
-        <v>14.638694309193614</v>
+        <v>14.943490633322106</v>
       </c>
       <c r="I28" s="35">
-        <v>1.6666666666666665</v>
+        <v>0.41666666666666663</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="3" t="s">
-        <v>294</v>
+        <v>206</v>
       </c>
       <c r="B29" s="35">
-        <v>72.705500000000001</v>
+        <v>70.221166666666647</v>
       </c>
       <c r="C29" s="6">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D29" s="35">
-        <v>59.259090407690564</v>
+        <v>60.211715871321665</v>
       </c>
       <c r="E29" s="6">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F29" s="35">
-        <v>28.271255555555555</v>
+        <v>24.013485185185186</v>
       </c>
       <c r="G29" s="35">
-        <v>75.477445858585853</v>
+        <v>70.05685656565656</v>
       </c>
       <c r="H29" s="35">
-        <v>14.37758632313551</v>
+        <v>14.638694309193614</v>
       </c>
       <c r="I29" s="35">
-        <v>0.33333333333333331</v>
+        <v>1.6666666666666665</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B30" s="35">
-        <v>71.904250000000005</v>
+        <v>69.735916666666654</v>
       </c>
       <c r="C30" s="6">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D30" s="35">
-        <v>59.516027511885113</v>
+        <v>62.572483664509093</v>
       </c>
       <c r="E30" s="6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F30" s="35">
-        <v>28.920703703703705</v>
+        <v>28.776481481481483</v>
       </c>
       <c r="G30" s="35">
-        <v>76.237274141414147</v>
+        <v>79.034913131313132</v>
       </c>
       <c r="H30" s="35">
-        <v>13.902003516161558</v>
+        <v>14.551249978286643</v>
       </c>
       <c r="I30" s="35">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="3" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="B31" s="35">
-        <v>76.911916666666656</v>
+        <v>68.705250000000007</v>
       </c>
       <c r="C31" s="6">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D31" s="35">
-        <v>60.308581724776019</v>
+        <v>61.060730239977097</v>
       </c>
       <c r="E31" s="6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F31" s="35">
-        <v>27.946374074074072</v>
+        <v>29.230225925925922</v>
       </c>
       <c r="G31" s="35">
-        <v>74.851016565656579</v>
+        <v>73.291786666666667</v>
       </c>
       <c r="H31" s="35">
-        <v>14.079840797841342</v>
+        <v>15.977784230606188</v>
       </c>
       <c r="I31" s="35">
-        <v>0.58333333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="3" t="s">
-        <v>297</v>
+        <v>13</v>
       </c>
       <c r="B32" s="35">
-        <v>77.376249999999985</v>
+        <v>68.316749999999999</v>
       </c>
       <c r="C32" s="6">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D32" s="35">
-        <v>59.336275056492923</v>
+        <v>59.839723124104147</v>
       </c>
       <c r="E32" s="6">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F32" s="35">
-        <v>28.862666666666669</v>
+        <v>29.888262962962958</v>
       </c>
       <c r="G32" s="35">
-        <v>68.463613333333328</v>
+        <v>79.32630040404041</v>
       </c>
       <c r="H32" s="35">
-        <v>13.743616389190937</v>
+        <v>15.019490611552243</v>
       </c>
       <c r="I32" s="35">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="3" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B33" s="35">
-        <v>72.547333333333327</v>
+        <v>68.228999999999999</v>
       </c>
       <c r="C33" s="6">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D33" s="35">
-        <v>59.839671819006689</v>
+        <v>60.010467967815742</v>
       </c>
       <c r="E33" s="6">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F33" s="35">
-        <v>29.086929629629633</v>
+        <v>30.554777777777772</v>
       </c>
       <c r="G33" s="35">
-        <v>65.699258383838384</v>
+        <v>62.940830303030296</v>
       </c>
       <c r="H33" s="35">
-        <v>14.004239416515457</v>
+        <v>14.178932504528932</v>
       </c>
       <c r="I33" s="35">
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="3" t="s">
-        <v>299</v>
+        <v>12</v>
       </c>
       <c r="B34" s="35">
-        <v>77.73</v>
+        <v>66.725499999999997</v>
       </c>
       <c r="C34" s="6">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="D34" s="35">
-        <v>59.906319719428815</v>
+        <v>60.705903136759709</v>
       </c>
       <c r="E34" s="6">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F34" s="35">
-        <v>27.89363333333333</v>
+        <v>27.318003703703702</v>
       </c>
       <c r="G34" s="35">
-        <v>70.693373737373733</v>
+        <v>70.954667878787888</v>
       </c>
       <c r="H34" s="35">
-        <v>14.160135152983383</v>
+        <v>15.359741396318265</v>
       </c>
       <c r="I34" s="35">
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="3" t="s">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="B35" s="35">
-        <v>76.731083333333331</v>
+        <v>57.294250000000005</v>
       </c>
       <c r="C35" s="6">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D35" s="35">
-        <v>60.204103486756672</v>
+        <v>58.796364843546087</v>
       </c>
       <c r="E35" s="6">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F35" s="35">
-        <v>27.597225925925922</v>
+        <v>30.724922222222226</v>
       </c>
       <c r="G35" s="35">
-        <v>72.766333535353539</v>
+        <v>101.27801474747476</v>
       </c>
       <c r="H35" s="35">
-        <v>14.145561872825617</v>
+        <v>15.333620398589836</v>
       </c>
       <c r="I35" s="35">
-        <v>0.33333333333333331</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" thickBot="1">
       <c r="A36" s="8" t="s">
-        <v>316</v>
+        <v>8</v>
       </c>
       <c r="B36" s="107">
-        <v>73.71008333333333</v>
+        <v>53.327749999999988</v>
       </c>
       <c r="C36" s="7">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D36" s="107">
-        <v>60.127627800663277</v>
+        <v>59.002716353076856</v>
       </c>
       <c r="E36" s="7">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F36" s="107">
-        <v>28.661070370370371</v>
+        <v>30.938296296296294</v>
       </c>
       <c r="G36" s="107">
-        <v>68.852888686868695</v>
+        <v>103.58700606060606</v>
       </c>
       <c r="H36" s="107">
-        <v>14.556307224927883</v>
+        <v>14.960898755279603</v>
       </c>
       <c r="I36" s="107">
-        <v>0.66666666666666663</v>
+        <v>2.416666666666667</v>
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
@@ -15597,6 +15604,9 @@
       <c r="K60" s="3"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:K36">
+    <sortCondition ref="C6:C36"/>
+  </sortState>
   <mergeCells count="4">
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D4:E4"/>
@@ -17284,43 +17294,43 @@
     <row r="4" spans="1:15" ht="15" customHeight="1">
       <c r="A4" s="27"/>
       <c r="B4" s="27"/>
-      <c r="C4" s="340" t="s">
+      <c r="C4" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="D4" s="340" t="s">
+      <c r="D4" s="341" t="s">
         <v>362</v>
       </c>
-      <c r="E4" s="344" t="s">
+      <c r="E4" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="F4" s="344" t="s">
+      <c r="F4" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="G4" s="344" t="s">
+      <c r="G4" s="345" t="s">
         <v>353</v>
       </c>
-      <c r="H4" s="344" t="s">
+      <c r="H4" s="345" t="s">
         <v>354</v>
       </c>
-      <c r="I4" s="344" t="s">
+      <c r="I4" s="345" t="s">
         <v>355</v>
       </c>
-      <c r="J4" s="344" t="s">
+      <c r="J4" s="345" t="s">
         <v>356</v>
       </c>
-      <c r="K4" s="344" t="s">
+      <c r="K4" s="345" t="s">
         <v>357</v>
       </c>
-      <c r="L4" s="344" t="s">
+      <c r="L4" s="345" t="s">
         <v>358</v>
       </c>
-      <c r="M4" s="344" t="s">
+      <c r="M4" s="345" t="s">
         <v>359</v>
       </c>
-      <c r="N4" s="344" t="s">
+      <c r="N4" s="345" t="s">
         <v>360</v>
       </c>
-      <c r="O4" s="342" t="s">
+      <c r="O4" s="343" t="s">
         <v>361</v>
       </c>
     </row>
@@ -17331,19 +17341,19 @@
       <c r="B5" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="341"/>
-      <c r="D5" s="341"/>
-      <c r="E5" s="345"/>
-      <c r="F5" s="345"/>
-      <c r="G5" s="345"/>
-      <c r="H5" s="345"/>
-      <c r="I5" s="345"/>
-      <c r="J5" s="345"/>
-      <c r="K5" s="345"/>
-      <c r="L5" s="345"/>
-      <c r="M5" s="345"/>
-      <c r="N5" s="345"/>
-      <c r="O5" s="343"/>
+      <c r="C5" s="342"/>
+      <c r="D5" s="342"/>
+      <c r="E5" s="346"/>
+      <c r="F5" s="346"/>
+      <c r="G5" s="346"/>
+      <c r="H5" s="346"/>
+      <c r="I5" s="346"/>
+      <c r="J5" s="346"/>
+      <c r="K5" s="346"/>
+      <c r="L5" s="346"/>
+      <c r="M5" s="346"/>
+      <c r="N5" s="346"/>
+      <c r="O5" s="344"/>
     </row>
     <row r="6" spans="1:15" ht="12.75" customHeight="1" thickTop="1">
       <c r="A6" s="13">
@@ -18880,19 +18890,19 @@
     <row r="3" spans="1:9">
       <c r="A3" s="38"/>
       <c r="B3" s="38"/>
-      <c r="C3" s="338" t="s">
+      <c r="C3" s="339" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="338"/>
+      <c r="D3" s="339"/>
       <c r="E3" s="9"/>
       <c r="F3" s="60" t="s">
         <v>95</v>
       </c>
       <c r="G3" s="9"/>
-      <c r="H3" s="338" t="s">
+      <c r="H3" s="339" t="s">
         <v>96</v>
       </c>
-      <c r="I3" s="338"/>
+      <c r="I3" s="339"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="38"/>
@@ -21673,17 +21683,17 @@
       <c r="N18" s="15"/>
     </row>
     <row r="19" spans="1:14" ht="23.25" customHeight="1">
-      <c r="A19" s="346" t="s">
+      <c r="A19" s="347" t="s">
         <v>123</v>
       </c>
-      <c r="B19" s="346"/>
-      <c r="C19" s="346"/>
-      <c r="D19" s="346"/>
-      <c r="E19" s="346"/>
-      <c r="F19" s="346"/>
-      <c r="G19" s="346"/>
-      <c r="H19" s="346"/>
-      <c r="I19" s="346"/>
+      <c r="B19" s="347"/>
+      <c r="C19" s="347"/>
+      <c r="D19" s="347"/>
+      <c r="E19" s="347"/>
+      <c r="F19" s="347"/>
+      <c r="G19" s="347"/>
+      <c r="H19" s="347"/>
+      <c r="I19" s="347"/>
       <c r="J19" s="69"/>
       <c r="K19" s="70"/>
       <c r="L19" s="71"/>
@@ -21853,17 +21863,17 @@
       <c r="I31" s="164"/>
     </row>
     <row r="32" spans="1:14" ht="23.25" customHeight="1">
-      <c r="A32" s="347" t="s">
+      <c r="A32" s="348" t="s">
         <v>408</v>
       </c>
-      <c r="B32" s="347"/>
-      <c r="C32" s="347"/>
-      <c r="D32" s="347"/>
-      <c r="E32" s="347"/>
-      <c r="F32" s="347"/>
-      <c r="G32" s="347"/>
-      <c r="H32" s="347"/>
-      <c r="I32" s="347"/>
+      <c r="B32" s="348"/>
+      <c r="C32" s="348"/>
+      <c r="D32" s="348"/>
+      <c r="E32" s="348"/>
+      <c r="F32" s="348"/>
+      <c r="G32" s="348"/>
+      <c r="H32" s="348"/>
+      <c r="I32" s="348"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -23014,25 +23024,25 @@
         <v>81</v>
       </c>
       <c r="B41" s="3"/>
-      <c r="C41" s="349">
+      <c r="C41" s="338">
         <v>23.125</v>
       </c>
-      <c r="D41" s="349">
+      <c r="D41" s="338">
         <v>90.555555555555557</v>
       </c>
-      <c r="E41" s="349">
+      <c r="E41" s="338">
         <v>19.029166666666669</v>
       </c>
-      <c r="F41" s="349">
+      <c r="F41" s="338">
         <v>18.226388888888888</v>
       </c>
-      <c r="G41" s="349">
+      <c r="G41" s="338">
         <v>11.101388888888888</v>
       </c>
-      <c r="H41" s="349">
+      <c r="H41" s="338">
         <v>17.972222222222221</v>
       </c>
-      <c r="I41" s="349">
+      <c r="I41" s="338">
         <v>4.1638888888888879</v>
       </c>
     </row>
@@ -24001,16 +24011,16 @@
         <v>81</v>
       </c>
       <c r="B41" s="3"/>
-      <c r="C41" s="349">
+      <c r="C41" s="338">
         <v>37.666666666666664</v>
       </c>
-      <c r="D41" s="349">
+      <c r="D41" s="338">
         <v>10.666197183098591</v>
       </c>
-      <c r="E41" s="349">
+      <c r="E41" s="338">
         <v>24.652777777777779</v>
       </c>
-      <c r="F41" s="349">
+      <c r="F41" s="338">
         <v>17.441666666666663</v>
       </c>
     </row>
@@ -27846,7 +27856,7 @@
     </row>
     <row r="41" spans="1:26" ht="141" customHeight="1">
       <c r="A41" s="13"/>
-      <c r="B41" s="348" t="s">
+      <c r="B41" s="349" t="s">
         <v>64</v>
       </c>
       <c r="C41" s="134" t="s">
@@ -27924,7 +27934,7 @@
     </row>
     <row r="42" spans="1:26" ht="141" customHeight="1">
       <c r="A42" s="13"/>
-      <c r="B42" s="348"/>
+      <c r="B42" s="349"/>
       <c r="C42" s="134" t="s">
         <v>141</v>
       </c>
@@ -35798,16 +35808,16 @@
       </c>
     </row>
     <row r="67" spans="1:53" ht="38.25" customHeight="1">
-      <c r="A67" s="351" t="s">
+      <c r="A67" s="350" t="s">
         <v>686</v>
       </c>
-      <c r="B67" s="351"/>
-      <c r="C67" s="351"/>
-      <c r="D67" s="351"/>
-      <c r="E67" s="351"/>
-      <c r="F67" s="351"/>
-      <c r="G67" s="351"/>
-      <c r="H67" s="351"/>
+      <c r="B67" s="350"/>
+      <c r="C67" s="350"/>
+      <c r="D67" s="350"/>
+      <c r="E67" s="350"/>
+      <c r="F67" s="350"/>
+      <c r="G67" s="350"/>
+      <c r="H67" s="350"/>
       <c r="I67" s="38"/>
       <c r="J67" s="38"/>
       <c r="K67" s="38"/>
@@ -35912,16 +35922,16 @@
       <c r="BA68" s="38"/>
     </row>
     <row r="69" spans="1:53" ht="25.5" customHeight="1">
-      <c r="A69" s="350" t="s">
+      <c r="A69" s="351" t="s">
         <v>688</v>
       </c>
-      <c r="B69" s="350"/>
-      <c r="C69" s="350"/>
-      <c r="D69" s="350"/>
-      <c r="E69" s="350"/>
-      <c r="F69" s="350"/>
-      <c r="G69" s="350"/>
-      <c r="H69" s="350"/>
+      <c r="B69" s="351"/>
+      <c r="C69" s="351"/>
+      <c r="D69" s="351"/>
+      <c r="E69" s="351"/>
+      <c r="F69" s="351"/>
+      <c r="G69" s="351"/>
+      <c r="H69" s="351"/>
       <c r="I69" s="38"/>
       <c r="J69" s="38"/>
       <c r="K69" s="38"/>
@@ -35969,16 +35979,16 @@
       <c r="BA69" s="38"/>
     </row>
     <row r="70" spans="1:53" ht="25.5" customHeight="1">
-      <c r="A70" s="350" t="s">
+      <c r="A70" s="351" t="s">
         <v>689</v>
       </c>
-      <c r="B70" s="350"/>
-      <c r="C70" s="350"/>
-      <c r="D70" s="350"/>
-      <c r="E70" s="350"/>
-      <c r="F70" s="350"/>
-      <c r="G70" s="350"/>
-      <c r="H70" s="350"/>
+      <c r="B70" s="351"/>
+      <c r="C70" s="351"/>
+      <c r="D70" s="351"/>
+      <c r="E70" s="351"/>
+      <c r="F70" s="351"/>
+      <c r="G70" s="351"/>
+      <c r="H70" s="351"/>
       <c r="I70" s="38"/>
       <c r="J70" s="38"/>
       <c r="K70" s="38"/>

--- a/data/2023_HRSWURN_Tables.xlsx
+++ b/data/2023_HRSWURN_Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARSMNSPP4DFG174\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\donoh132\Box\IWG_Breeding\Git_demo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57E4D5B-FAEA-4C0F-9AEA-2ABB4A1B0A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A7A450-8FC9-4E64-A2ED-8ED490FCBBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="838" firstSheet="15" activeTab="26" xr2:uid="{BC65913E-1809-4B59-BE8F-B0869AF7DC59}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="838" firstSheet="18" activeTab="27" xr2:uid="{BC65913E-1809-4B59-BE8F-B0869AF7DC59}"/>
   </bookViews>
   <sheets>
     <sheet name="Entry List" sheetId="1" r:id="rId1"/>
@@ -40,6 +40,7 @@
     <sheet name="MarkerTrait data" sheetId="23" r:id="rId25"/>
     <sheet name="Marker info" sheetId="30" r:id="rId26"/>
     <sheet name="African stem rust" sheetId="36" r:id="rId27"/>
+    <sheet name="Sheet1" sheetId="37" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4582" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4583" uniqueCount="751">
   <si>
     <t>Entry</t>
   </si>
@@ -3412,6 +3413,9 @@
   </si>
   <si>
     <t>Previous crop: Flax. Soil type: Williams-Bowbells loam. Rainfall: 7.8 inches (4/26 - 8/16)</t>
+  </si>
+  <si>
+    <t>Hannah testing</t>
   </si>
 </sst>
 </file>
@@ -5839,6 +5843,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5872,14 +5879,11 @@
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="126">
@@ -14240,14 +14244,14 @@
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="339" t="s">
+      <c r="B3" s="340" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="339"/>
-      <c r="D3" s="339" t="s">
+      <c r="C3" s="340"/>
+      <c r="D3" s="340" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="339"/>
+      <c r="E3" s="340"/>
       <c r="F3" s="31" t="s">
         <v>71</v>
       </c>
@@ -14265,14 +14269,14 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="2"/>
-      <c r="B4" s="339" t="s">
+      <c r="B4" s="340" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="339"/>
-      <c r="D4" s="339" t="s">
+      <c r="C4" s="340"/>
+      <c r="D4" s="340" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="339"/>
+      <c r="E4" s="340"/>
       <c r="F4" s="31" t="s">
         <v>77</v>
       </c>
@@ -17284,43 +17288,43 @@
     <row r="4" spans="1:15" ht="15" customHeight="1">
       <c r="A4" s="27"/>
       <c r="B4" s="27"/>
-      <c r="C4" s="340" t="s">
+      <c r="C4" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="D4" s="340" t="s">
+      <c r="D4" s="341" t="s">
         <v>362</v>
       </c>
-      <c r="E4" s="344" t="s">
+      <c r="E4" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="F4" s="344" t="s">
+      <c r="F4" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="G4" s="344" t="s">
+      <c r="G4" s="345" t="s">
         <v>353</v>
       </c>
-      <c r="H4" s="344" t="s">
+      <c r="H4" s="345" t="s">
         <v>354</v>
       </c>
-      <c r="I4" s="344" t="s">
+      <c r="I4" s="345" t="s">
         <v>355</v>
       </c>
-      <c r="J4" s="344" t="s">
+      <c r="J4" s="345" t="s">
         <v>356</v>
       </c>
-      <c r="K4" s="344" t="s">
+      <c r="K4" s="345" t="s">
         <v>357</v>
       </c>
-      <c r="L4" s="344" t="s">
+      <c r="L4" s="345" t="s">
         <v>358</v>
       </c>
-      <c r="M4" s="344" t="s">
+      <c r="M4" s="345" t="s">
         <v>359</v>
       </c>
-      <c r="N4" s="344" t="s">
+      <c r="N4" s="345" t="s">
         <v>360</v>
       </c>
-      <c r="O4" s="342" t="s">
+      <c r="O4" s="343" t="s">
         <v>361</v>
       </c>
     </row>
@@ -17331,19 +17335,19 @@
       <c r="B5" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="341"/>
-      <c r="D5" s="341"/>
-      <c r="E5" s="345"/>
-      <c r="F5" s="345"/>
-      <c r="G5" s="345"/>
-      <c r="H5" s="345"/>
-      <c r="I5" s="345"/>
-      <c r="J5" s="345"/>
-      <c r="K5" s="345"/>
-      <c r="L5" s="345"/>
-      <c r="M5" s="345"/>
-      <c r="N5" s="345"/>
-      <c r="O5" s="343"/>
+      <c r="C5" s="342"/>
+      <c r="D5" s="342"/>
+      <c r="E5" s="346"/>
+      <c r="F5" s="346"/>
+      <c r="G5" s="346"/>
+      <c r="H5" s="346"/>
+      <c r="I5" s="346"/>
+      <c r="J5" s="346"/>
+      <c r="K5" s="346"/>
+      <c r="L5" s="346"/>
+      <c r="M5" s="346"/>
+      <c r="N5" s="346"/>
+      <c r="O5" s="344"/>
     </row>
     <row r="6" spans="1:15" ht="12.75" customHeight="1" thickTop="1">
       <c r="A6" s="13">
@@ -18880,19 +18884,19 @@
     <row r="3" spans="1:9">
       <c r="A3" s="38"/>
       <c r="B3" s="38"/>
-      <c r="C3" s="338" t="s">
+      <c r="C3" s="339" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="338"/>
+      <c r="D3" s="339"/>
       <c r="E3" s="9"/>
       <c r="F3" s="60" t="s">
         <v>95</v>
       </c>
       <c r="G3" s="9"/>
-      <c r="H3" s="338" t="s">
+      <c r="H3" s="339" t="s">
         <v>96</v>
       </c>
-      <c r="I3" s="338"/>
+      <c r="I3" s="339"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="38"/>
@@ -21673,17 +21677,17 @@
       <c r="N18" s="15"/>
     </row>
     <row r="19" spans="1:14" ht="23.25" customHeight="1">
-      <c r="A19" s="346" t="s">
+      <c r="A19" s="347" t="s">
         <v>123</v>
       </c>
-      <c r="B19" s="346"/>
-      <c r="C19" s="346"/>
-      <c r="D19" s="346"/>
-      <c r="E19" s="346"/>
-      <c r="F19" s="346"/>
-      <c r="G19" s="346"/>
-      <c r="H19" s="346"/>
-      <c r="I19" s="346"/>
+      <c r="B19" s="347"/>
+      <c r="C19" s="347"/>
+      <c r="D19" s="347"/>
+      <c r="E19" s="347"/>
+      <c r="F19" s="347"/>
+      <c r="G19" s="347"/>
+      <c r="H19" s="347"/>
+      <c r="I19" s="347"/>
       <c r="J19" s="69"/>
       <c r="K19" s="70"/>
       <c r="L19" s="71"/>
@@ -21853,17 +21857,17 @@
       <c r="I31" s="164"/>
     </row>
     <row r="32" spans="1:14" ht="23.25" customHeight="1">
-      <c r="A32" s="347" t="s">
+      <c r="A32" s="348" t="s">
         <v>408</v>
       </c>
-      <c r="B32" s="347"/>
-      <c r="C32" s="347"/>
-      <c r="D32" s="347"/>
-      <c r="E32" s="347"/>
-      <c r="F32" s="347"/>
-      <c r="G32" s="347"/>
-      <c r="H32" s="347"/>
-      <c r="I32" s="347"/>
+      <c r="B32" s="348"/>
+      <c r="C32" s="348"/>
+      <c r="D32" s="348"/>
+      <c r="E32" s="348"/>
+      <c r="F32" s="348"/>
+      <c r="G32" s="348"/>
+      <c r="H32" s="348"/>
+      <c r="I32" s="348"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -23014,25 +23018,25 @@
         <v>81</v>
       </c>
       <c r="B41" s="3"/>
-      <c r="C41" s="349">
+      <c r="C41" s="338">
         <v>23.125</v>
       </c>
-      <c r="D41" s="349">
+      <c r="D41" s="338">
         <v>90.555555555555557</v>
       </c>
-      <c r="E41" s="349">
+      <c r="E41" s="338">
         <v>19.029166666666669</v>
       </c>
-      <c r="F41" s="349">
+      <c r="F41" s="338">
         <v>18.226388888888888</v>
       </c>
-      <c r="G41" s="349">
+      <c r="G41" s="338">
         <v>11.101388888888888</v>
       </c>
-      <c r="H41" s="349">
+      <c r="H41" s="338">
         <v>17.972222222222221</v>
       </c>
-      <c r="I41" s="349">
+      <c r="I41" s="338">
         <v>4.1638888888888879</v>
       </c>
     </row>
@@ -24001,16 +24005,16 @@
         <v>81</v>
       </c>
       <c r="B41" s="3"/>
-      <c r="C41" s="349">
+      <c r="C41" s="338">
         <v>37.666666666666664</v>
       </c>
-      <c r="D41" s="349">
+      <c r="D41" s="338">
         <v>10.666197183098591</v>
       </c>
-      <c r="E41" s="349">
+      <c r="E41" s="338">
         <v>24.652777777777779</v>
       </c>
-      <c r="F41" s="349">
+      <c r="F41" s="338">
         <v>17.441666666666663</v>
       </c>
     </row>
@@ -27846,7 +27850,7 @@
     </row>
     <row r="41" spans="1:26" ht="141" customHeight="1">
       <c r="A41" s="13"/>
-      <c r="B41" s="348" t="s">
+      <c r="B41" s="349" t="s">
         <v>64</v>
       </c>
       <c r="C41" s="134" t="s">
@@ -27924,7 +27928,7 @@
     </row>
     <row r="42" spans="1:26" ht="141" customHeight="1">
       <c r="A42" s="13"/>
-      <c r="B42" s="348"/>
+      <c r="B42" s="349"/>
       <c r="C42" s="134" t="s">
         <v>141</v>
       </c>
@@ -35798,16 +35802,16 @@
       </c>
     </row>
     <row r="67" spans="1:53" ht="38.25" customHeight="1">
-      <c r="A67" s="351" t="s">
+      <c r="A67" s="350" t="s">
         <v>686</v>
       </c>
-      <c r="B67" s="351"/>
-      <c r="C67" s="351"/>
-      <c r="D67" s="351"/>
-      <c r="E67" s="351"/>
-      <c r="F67" s="351"/>
-      <c r="G67" s="351"/>
-      <c r="H67" s="351"/>
+      <c r="B67" s="350"/>
+      <c r="C67" s="350"/>
+      <c r="D67" s="350"/>
+      <c r="E67" s="350"/>
+      <c r="F67" s="350"/>
+      <c r="G67" s="350"/>
+      <c r="H67" s="350"/>
       <c r="I67" s="38"/>
       <c r="J67" s="38"/>
       <c r="K67" s="38"/>
@@ -35912,16 +35916,16 @@
       <c r="BA68" s="38"/>
     </row>
     <row r="69" spans="1:53" ht="25.5" customHeight="1">
-      <c r="A69" s="350" t="s">
+      <c r="A69" s="351" t="s">
         <v>688</v>
       </c>
-      <c r="B69" s="350"/>
-      <c r="C69" s="350"/>
-      <c r="D69" s="350"/>
-      <c r="E69" s="350"/>
-      <c r="F69" s="350"/>
-      <c r="G69" s="350"/>
-      <c r="H69" s="350"/>
+      <c r="B69" s="351"/>
+      <c r="C69" s="351"/>
+      <c r="D69" s="351"/>
+      <c r="E69" s="351"/>
+      <c r="F69" s="351"/>
+      <c r="G69" s="351"/>
+      <c r="H69" s="351"/>
       <c r="I69" s="38"/>
       <c r="J69" s="38"/>
       <c r="K69" s="38"/>
@@ -35969,16 +35973,16 @@
       <c r="BA69" s="38"/>
     </row>
     <row r="70" spans="1:53" ht="25.5" customHeight="1">
-      <c r="A70" s="350" t="s">
+      <c r="A70" s="351" t="s">
         <v>689</v>
       </c>
-      <c r="B70" s="350"/>
-      <c r="C70" s="350"/>
-      <c r="D70" s="350"/>
-      <c r="E70" s="350"/>
-      <c r="F70" s="350"/>
-      <c r="G70" s="350"/>
-      <c r="H70" s="350"/>
+      <c r="B70" s="351"/>
+      <c r="C70" s="351"/>
+      <c r="D70" s="351"/>
+      <c r="E70" s="351"/>
+      <c r="F70" s="351"/>
+      <c r="G70" s="351"/>
+      <c r="H70" s="351"/>
       <c r="I70" s="38"/>
       <c r="J70" s="38"/>
       <c r="K70" s="38"/>
@@ -36231,6 +36235,21 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79DBE69-9EA5-4910-8382-7DB3FFCE54DB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E61D2DC-DC32-47AE-9144-9665F814590A}">
   <dimension ref="A1:G47"/>
